--- a/hospice_forms/015_hospice_care_records_release_form--hospice_forms.xlsx
+++ b/hospice_forms/015_hospice_care_records_release_form--hospice_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'dr._smith'}</t>
+          <t>dr._smith</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Dr. Smith'}</t>
+          <t>Dr. Smith</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'dr._johnson'}</t>
+          <t>dr._johnson</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Dr. Johnson'}</t>
+          <t>Dr. Johnson</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'dr._doe'}</t>
+          <t>dr._doe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Dr. Doe'}</t>
+          <t>Dr. Doe</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'morphine'}</t>
+          <t>morphine</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Morphine'}</t>
+          <t>Morphine</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'oxycontin'}</t>
+          <t>oxycontin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Oxycontin'}</t>
+          <t>Oxycontin</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'amlodipine'}</t>
+          <t>amlodipine</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Amlodipine'}</t>
+          <t>Amlodipine</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'heart_failure'}</t>
+          <t>heart_failure</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Heart failure'}</t>
+          <t>Heart failure</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'diabetes'}</t>
+          <t>diabetes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Diabetes'}</t>
+          <t>Diabetes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'asthma'}</t>
+          <t>asthma</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Asthma'}</t>
+          <t>Asthma</t>
         </is>
       </c>
     </row>
